--- a/data/aed_location/data.xlsx
+++ b/data/aed_location/data.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L446"/>
+  <dimension ref="A1:L449"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -17359,9 +17359,69 @@
         <v/>
       </c>
     </row>
+    <row r="447">
+      <c r="A447" t="str">
+        <v>540</v>
+      </c>
+      <c r="B447" t="str">
+        <v>34.358723744025994</v>
+      </c>
+      <c r="C447" t="str">
+        <v>133.96879857371403</v>
+      </c>
+      <c r="D447" t="str">
+        <v>高松市下笠居コミュニティセンター</v>
+      </c>
+      <c r="E447" t="str">
+        <v>高松市生島町353-1</v>
+      </c>
+      <c r="F447" t="str">
+        <v>正面玄関右壁面</v>
+      </c>
+    </row>
+    <row r="448">
+      <c r="A448" t="str">
+        <v>541</v>
+      </c>
+      <c r="B448" t="str">
+        <v>34.32701926691553</v>
+      </c>
+      <c r="C448" t="str">
+        <v>134.09174376489153</v>
+      </c>
+      <c r="D448" t="str">
+        <v>高松市古高松南コミュニティセンター</v>
+      </c>
+      <c r="E448" t="str">
+        <v>高松市春日町782-2</v>
+      </c>
+      <c r="F448" t="str">
+        <v>1階廊下</v>
+      </c>
+    </row>
+    <row r="449">
+      <c r="A449" t="str">
+        <v>542</v>
+      </c>
+      <c r="B449" t="str">
+        <v>34.336105094782226</v>
+      </c>
+      <c r="C449" t="str">
+        <v>134.05686145760404</v>
+      </c>
+      <c r="D449" t="str">
+        <v>高松市花園コミュニティセンター</v>
+      </c>
+      <c r="E449" t="str">
+        <v>高松市観光通2-8-9</v>
+      </c>
+      <c r="F449" t="str">
+        <v>２階玄関　靴箱上</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L446"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L449"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/aed_location/data.xlsx
+++ b/data/aed_location/data.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L449"/>
+  <dimension ref="A1:L451"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -17378,6 +17378,24 @@
       <c r="F447" t="str">
         <v>正面玄関右壁面</v>
       </c>
+      <c r="G447" t="str">
+        <v/>
+      </c>
+      <c r="H447" t="str">
+        <v/>
+      </c>
+      <c r="I447" t="str">
+        <v/>
+      </c>
+      <c r="J447" t="str">
+        <v/>
+      </c>
+      <c r="K447" t="str">
+        <v/>
+      </c>
+      <c r="L447" t="str">
+        <v/>
+      </c>
     </row>
     <row r="448">
       <c r="A448" t="str">
@@ -17398,6 +17416,24 @@
       <c r="F448" t="str">
         <v>1階廊下</v>
       </c>
+      <c r="G448" t="str">
+        <v/>
+      </c>
+      <c r="H448" t="str">
+        <v/>
+      </c>
+      <c r="I448" t="str">
+        <v/>
+      </c>
+      <c r="J448" t="str">
+        <v/>
+      </c>
+      <c r="K448" t="str">
+        <v/>
+      </c>
+      <c r="L448" t="str">
+        <v/>
+      </c>
     </row>
     <row r="449">
       <c r="A449" t="str">
@@ -17418,10 +17454,92 @@
       <c r="F449" t="str">
         <v>２階玄関　靴箱上</v>
       </c>
+      <c r="G449" t="str">
+        <v/>
+      </c>
+      <c r="H449" t="str">
+        <v/>
+      </c>
+      <c r="I449" t="str">
+        <v/>
+      </c>
+      <c r="J449" t="str">
+        <v/>
+      </c>
+      <c r="K449" t="str">
+        <v/>
+      </c>
+      <c r="L449" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="450">
+      <c r="A450" t="str">
+        <v>543</v>
+      </c>
+      <c r="B450" t="str">
+        <v>34.34393128061774</v>
+      </c>
+      <c r="C450" t="str">
+        <v>134.0336242718585</v>
+      </c>
+      <c r="D450" t="str">
+        <v>東洋建設株式会社　四国支店</v>
+      </c>
+      <c r="E450" t="str">
+        <v>高松市昭和町一丁目3番5号</v>
+      </c>
+      <c r="F450" t="str">
+        <v>１階正面玄関前</v>
+      </c>
+      <c r="G450" t="str">
+        <v>087-861-1184</v>
+      </c>
+      <c r="H450" t="str">
+        <v>月火水木金土日</v>
+      </c>
+      <c r="I450" t="str">
+        <v>0:00</v>
+      </c>
+      <c r="J450" t="str">
+        <v>24:00</v>
+      </c>
+    </row>
+    <row r="451">
+      <c r="A451" t="str">
+        <v>544</v>
+      </c>
+      <c r="B451" t="str">
+        <v>34.27397818768149</v>
+      </c>
+      <c r="C451" t="str">
+        <v>134.10475416810442</v>
+      </c>
+      <c r="D451" t="str">
+        <v>高松市十河コミュニティセンター</v>
+      </c>
+      <c r="E451" t="str">
+        <v>高松市十川西町299‐1</v>
+      </c>
+      <c r="F451" t="str">
+        <v>玄関横</v>
+      </c>
+      <c r="G451" t="str">
+        <v>087-848-0166</v>
+      </c>
+      <c r="H451" t="str">
+        <v>平日</v>
+      </c>
+      <c r="I451" t="str">
+        <v>9:00</v>
+      </c>
+      <c r="J451" t="str">
+        <v>17:00</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L449"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L451"/>
   </ignoredErrors>
 </worksheet>
 </file>